--- a/backend/wp_templates/G/G10 交易性金融负债.xlsx
+++ b/backend/wp_templates/G/G10 交易性金融负债.xlsx
@@ -15919,11 +15919,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="196">
-        <f>G8-D9</f>
+        <f>G9-D9</f>
         <v>0</v>
       </c>
       <c r="I9" s="195" t="str">
-        <f>IF(AND(D9=0,G8=0),"",IF(AND(D9=0,G8&gt;0),1,H9/D9))</f>
+        <f>IF(AND(D9=0,G9=0),"",IF(AND(D9=0,G9&gt;0),1,H9/D9))</f>
         <v/>
       </c>
       <c r="J9" s="294"/>
@@ -16495,7 +16495,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="193">
-        <f>G8+G19</f>
+        <f>G9+G19</f>
         <v>0</v>
       </c>
       <c r="H29" s="193">
